--- a/RaidenDemo/文档/配置表/PlayerAircraftResource.xlsx
+++ b/RaidenDemo/文档/配置表/PlayerAircraftResource.xlsx
@@ -470,198 +470,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="20" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" s="5" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="5" t="str">
-        <x:v>code</x:v>
-      </x:c>
-      <x:c r="D1" s="5" t="str">
-        <x:v>displayName</x:v>
-      </x:c>
-      <x:c r="E1" s="5" t="str">
-        <x:v>maxLevel</x:v>
-      </x:c>
-      <x:c r="F1" s="31" t="str">
-        <x:v>defaultUnlocked</x:v>
-      </x:c>
-      <x:c r="G1" s="31" t="str">
-        <x:v>unlockStarCost</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="20" customHeight="1">
-      <x:c r="A2" s="10" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B2" s="10" t="str">
-        <x:v>飞机类型ID</x:v>
-      </x:c>
-      <x:c r="C2" s="10" t="str">
-        <x:v>稳定编码</x:v>
-      </x:c>
-      <x:c r="D2" s="10" t="str">
-        <x:v>显示名称</x:v>
-      </x:c>
-      <x:c r="E2" s="10" t="str">
-        <x:v>等级上限</x:v>
-      </x:c>
-      <x:c r="F2" s="37" t="str">
-        <x:v>默认解锁</x:v>
-      </x:c>
-      <x:c r="G2" s="37" t="str">
-        <x:v>解锁星数</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="20" customHeight="1">
-      <x:c r="A3" s="10" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C3" s="10" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="D3" s="10" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="E3" s="10" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F3" s="37" t="str">
-        <x:v>bool</x:v>
-      </x:c>
-      <x:c r="G3" s="37" t="str">
-        <x:v>int</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="20" customHeight="1">
-      <x:c r="A4" s="20"/>
-      <x:c r="B4" s="20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="20" t="str">
-        <x:v>player_aircraft_assault_001</x:v>
-      </x:c>
-      <x:c r="D4" s="20" t="str">
-        <x:v>突击型战机</x:v>
-      </x:c>
-      <x:c r="E4" s="20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F4" s="48" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G4" s="49" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="24"/>
-      <x:c r="B5" s="24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="24" t="str">
-        <x:v>player_aircraft_heavy_001</x:v>
-      </x:c>
-      <x:c r="D5" s="24" t="str">
-        <x:v>重装型战机</x:v>
-      </x:c>
-      <x:c r="E5" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F5" s="48" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="49" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="24"/>
-      <x:c r="B6" s="24" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="24" t="str">
-        <x:v>player_aircraft_swift_001</x:v>
-      </x:c>
-      <x:c r="D6" s="24" t="str">
-        <x:v>迅捷型战机</x:v>
-      </x:c>
-      <x:c r="E6" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F6" s="48" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="49" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="24"/>
-      <x:c r="B7" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="24" t="str">
-        <x:v>player_aircraft_spread_001</x:v>
-      </x:c>
-      <x:c r="D7" s="24" t="str">
-        <x:v>散射型战机</x:v>
-      </x:c>
-      <x:c r="E7" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F7" s="48" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="49" t="n">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="24"/>
-      <x:c r="B8" s="24" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="24" t="str">
-        <x:v>player_aircraft_beam_001</x:v>
-      </x:c>
-      <x:c r="D8" s="24" t="str">
-        <x:v>聚能型战机</x:v>
-      </x:c>
-      <x:c r="E8" s="24" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F8" s="48" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="49" t="n">
-        <x:v>6</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F4:F1048576">
-      <x:formula1>"true,false"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="15" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="5" t="str">
+        <v>##var</v>
+      </c>
+      <c r="B1" s="5" t="str">
+        <v>id</v>
+      </c>
+      <c r="C1" s="5" t="str">
+        <v>code</v>
+      </c>
+      <c r="D1" s="5" t="str">
+        <v>displayName</v>
+      </c>
+      <c r="E1" s="5" t="str">
+        <v>maxLevel</v>
+      </c>
+      <c r="F1" s="31" t="str">
+        <v>defaultUnlocked</v>
+      </c>
+      <c r="G1" s="31" t="str">
+        <v>unlockStarCost</v>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="10" t="str">
+        <v>##</v>
+      </c>
+      <c r="B2" s="10" t="str">
+        <v>飞机类型ID</v>
+      </c>
+      <c r="C2" s="10" t="str">
+        <v>稳定编码</v>
+      </c>
+      <c r="D2" s="10" t="str">
+        <v>显示名称</v>
+      </c>
+      <c r="E2" s="10" t="str">
+        <v>等级上限</v>
+      </c>
+      <c r="F2" s="37" t="str">
+        <v>默认解锁</v>
+      </c>
+      <c r="G2" s="37" t="str">
+        <v>解锁星数</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="10" t="str">
+        <v>##type</v>
+      </c>
+      <c r="B3" s="10" t="str">
+        <v>int</v>
+      </c>
+      <c r="C3" s="10" t="str">
+        <v>string</v>
+      </c>
+      <c r="D3" s="10" t="str">
+        <v>string</v>
+      </c>
+      <c r="E3" s="10" t="str">
+        <v>int</v>
+      </c>
+      <c r="F3" s="37" t="str">
+        <v>bool</v>
+      </c>
+      <c r="G3" s="37" t="str">
+        <v>int</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="20"/>
+      <c r="B4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20" t="str">
+        <v>player_aircraft_assault_001</v>
+      </c>
+      <c r="D4" s="20" t="str">
+        <v>突击型战机</v>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="24" t="str">
+        <v>player_aircraft_heavy_001</v>
+      </c>
+      <c r="D5" s="24" t="str">
+        <v>重装型战机</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="24" t="str">
+        <v>player_aircraft_swift_001</v>
+      </c>
+      <c r="D6" s="24" t="str">
+        <v>迅捷型战机</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="24" t="str">
+        <v>player_aircraft_spread_001</v>
+      </c>
+      <c r="D7" s="24" t="str">
+        <v>散射型战机</v>
+      </c>
+      <c r="E7" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24"/>
+      <c r="B8" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="24" t="str">
+        <v>player_aircraft_beam_001</v>
+      </c>
+      <c r="D8" s="24" t="str">
+        <v>聚能型战机</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F8" s="48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="49" t="n">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="F4:F1048576">
+      <formula1>"true,false"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>